--- a/sheets/조재수대금교본/검수/한오백년.xlsx
+++ b/sheets/조재수대금교본/검수/한오백년.xlsx
@@ -5141,7 +5141,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∽</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="E3" s="22"/>
@@ -5165,7 +5165,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㄱ</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -5213,9 +5213,8 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-㳞
-‹</t>
+          <t xml:space="preserve">汰
+㳞</t>
         </is>
       </c>
       <c r="C5" s="24"/>
@@ -5223,24 +5222,22 @@
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太∧
-仲
-‹</t>
+          <t xml:space="preserve">太
+仲</t>
         </is>
       </c>
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃ʒ
+          <t xml:space="preserve">黃
 㑲黃</t>
         </is>
       </c>
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太∧
-仲
-‹</t>
+          <t xml:space="preserve">太
+仲</t>
         </is>
       </c>
       <c r="K5" s="24"/>
@@ -5248,15 +5245,14 @@
       <c r="M5" s="24"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太∧
-仲
-‹</t>
+          <t xml:space="preserve">太
+仲</t>
         </is>
       </c>
       <c r="O5" s="24"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃ʒ
+          <t xml:space="preserve">黃
 㑲黃</t>
         </is>
       </c>
@@ -5280,7 +5276,7 @@
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄱ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="G6" s="22"/>
@@ -5292,7 +5288,7 @@
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄱ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="K6" s="22"/>
@@ -5305,7 +5301,7 @@
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄱ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="O6" s="22"/>
@@ -5333,8 +5329,7 @@
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-⌝</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="G7" s="23"/>
@@ -5342,8 +5337,7 @@
       <c r="I7" s="23"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-⌝</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="K7" s="23"/>
@@ -5355,8 +5349,7 @@
       <c r="M7" s="23"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-⌝</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="O7" s="23"/>
@@ -5368,62 +5361,54 @@
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢
-南
-‹</t>
+南</t>
         </is>
       </c>
       <c r="C8" s="24"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太⌝
-㑲
-‹</t>
+          <t xml:space="preserve">太
+㑲</t>
         </is>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太∧
-仲
-‹</t>
+          <t xml:space="preserve">太
+仲</t>
         </is>
       </c>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太⌝
-㑲
-‹</t>
+          <t xml:space="preserve">太
+㑲</t>
         </is>
       </c>
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太⌝
-㑲
-‹</t>
+          <t xml:space="preserve">太
+㑲</t>
         </is>
       </c>
       <c r="O8" s="24"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太∧
-仲
-‹</t>
+          <t xml:space="preserve">太
+仲</t>
         </is>
       </c>
       <c r="Q8" s="24"/>
@@ -5439,7 +5424,7 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="E9" s="22"/>
@@ -5451,7 +5436,7 @@
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄱ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I9" s="22"/>
@@ -5463,7 +5448,7 @@
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄱ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="M9" s="22"/>
@@ -5475,18 +5460,14 @@
       <c r="O9" s="22"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㄱ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="Q9" s="22"/>
     </row>
     <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="B10" s="21"/>
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
@@ -5510,8 +5491,7 @@
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="K10" s="23"/>
@@ -5546,53 +5526,49 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ʒ
-–
-ﾉ</t>
+          <t xml:space="preserve">㳞
+–</t>
         </is>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲ʒ
-ﾉ‹</t>
+仲</t>
         </is>
       </c>
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲ʒ
-–ﾉ</t>
+          <t xml:space="preserve">仲
+–</t>
         </is>
       </c>
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲ʒ
-ﾉ</t>
+仲</t>
         </is>
       </c>
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲ʒ
-–
-ﾉ</t>
+          <t xml:space="preserve">仲
+–</t>
         </is>
       </c>
       <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲ʒ</t>
+仲</t>
         </is>
       </c>
       <c r="O11" s="24"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲ʒ
+          <t xml:space="preserve">仲
 –</t>
         </is>
       </c>
@@ -5602,21 +5578,20 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄷ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
+          <t xml:space="preserve">汰
 南</t>
         </is>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ㅋ
-∽</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -5629,21 +5604,20 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ㅋ∽</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太⌝
+          <t xml:space="preserve">太
 㑲</t>
         </is>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ㅋ
-∽</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="O12" s="22"/>
@@ -5697,23 +5671,17 @@
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
-南ㄴ
-‹</t>
+          <t xml:space="preserve">潢
+南</t>
         </is>
       </c>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
-㑲黃
-‹</t>
+          <t xml:space="preserve">潢
+㑲黃</t>
         </is>
       </c>
       <c r="I14" s="24"/>
@@ -5726,20 +5694,16 @@
       <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃ʒ
+          <t xml:space="preserve">黃
 㑲黃</t>
         </is>
       </c>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
+          <t xml:space="preserve">潢
 㑲黃</t>
         </is>
       </c>
@@ -5820,7 +5784,7 @@
       <c r="J18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–潢ʒ</t>
+–潢</t>
         </is>
       </c>
       <c r="K18" s="23"/>
@@ -5829,7 +5793,7 @@
       <c r="N18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–潢ʒ</t>
+–潢</t>
         </is>
       </c>
       <c r="O18" s="23"/>
@@ -5866,11 +5830,7 @@
         </is>
       </c>
       <c r="O19" s="24"/>
-      <c r="P19" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P19" s="21"/>
       <c r="Q19" s="24"/>
     </row>
     <row r="20" ht="96.05" customHeight="true">
@@ -5885,7 +5845,7 @@
       <c r="I20" s="22"/>
       <c r="J20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄷ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="K20" s="22"/>
@@ -5898,7 +5858,7 @@
       <c r="M20" s="22"/>
       <c r="N20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄷ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="O20" s="22"/>
@@ -5922,24 +5882,22 @@
       <c r="I21" s="23"/>
       <c r="J21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
-–
-ﾉ</t>
+          <t xml:space="preserve">潢
+–</t>
         </is>
       </c>
       <c r="K21" s="23"/>
       <c r="L21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–Z∧</t>
+–</t>
         </is>
       </c>
       <c r="M21" s="23"/>
       <c r="N21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
-–
-ﾉ</t>
+          <t xml:space="preserve">潢
+–</t>
         </is>
       </c>
       <c r="O21" s="23"/>
@@ -5963,9 +5921,8 @@
       <c r="I22" s="24"/>
       <c r="J22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南⌝
-姑
-‹</t>
+          <t xml:space="preserve">南
+姑</t>
         </is>
       </c>
       <c r="K22" s="24"/>
@@ -5978,17 +5935,15 @@
       <c r="M22" s="24"/>
       <c r="N22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南⌝
-姑
-‹</t>
+          <t xml:space="preserve">南
+姑</t>
         </is>
       </c>
       <c r="O22" s="24"/>
       <c r="P22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∧
-潢
-‹</t>
+          <t xml:space="preserve">南
+潢</t>
         </is>
       </c>
       <c r="Q22" s="24"/>
@@ -6005,7 +5960,7 @@
       <c r="I23" s="22"/>
       <c r="J23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南潢ㅂ
+          <t xml:space="preserve">南潢
 –</t>
         </is>
       </c>
@@ -6044,7 +5999,7 @@
       <c r="J24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–㴌
-潢ﾉ</t>
+潢</t>
         </is>
       </c>
       <c r="K24" s="23"/>
@@ -6056,8 +6011,7 @@
       <c r="M24" s="23"/>
       <c r="N24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z∧
-潢</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="O24" s="23"/>
@@ -6081,29 +6035,28 @@
       <c r="J25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-ㅂ∼
-‹</t>
+∼</t>
         </is>
       </c>
       <c r="K25" s="24"/>
       <c r="L25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
-–ﾉ</t>
+          <t xml:space="preserve">潢
+–</t>
         </is>
       </c>
       <c r="M25" s="24"/>
       <c r="N25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢ʒ</t>
+潢</t>
         </is>
       </c>
       <c r="O25" s="24"/>
       <c r="P25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
-–ﾉ</t>
+          <t xml:space="preserve">潢
+–</t>
         </is>
       </c>
       <c r="Q25" s="24"/>
@@ -6120,27 +6073,27 @@
       <c r="I26" s="22"/>
       <c r="J26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ﾉ
-潢ㅂ∼</t>
+          <t xml:space="preserve">潢
+潢∼</t>
         </is>
       </c>
       <c r="K26" s="22"/>
       <c r="L26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南⌝
+          <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
       <c r="M26" s="22"/>
       <c r="N26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∽</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="O26" s="22"/>
       <c r="P26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南⌝
+          <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
@@ -6158,7 +6111,7 @@
       <c r="I27" s="23"/>
       <c r="J27" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南ㅂ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="K27" s="23"/>
@@ -6196,23 +6149,14 @@
       <c r="K28" s="24"/>
       <c r="L28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南⌝
-姑
-‹</t>
+          <t xml:space="preserve">南
+姑</t>
         </is>
       </c>
       <c r="M28" s="24"/>
-      <c r="N28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N28" s="21"/>
       <c r="O28" s="24"/>
-      <c r="P28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P28" s="21"/>
       <c r="Q28" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/한오백년.xlsx
+++ b/sheets/조재수대금교본/검수/한오백년.xlsx
@@ -5141,7 +5141,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∽</t>
         </is>
       </c>
       <c r="E3" s="22"/>
@@ -5165,7 +5165,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林ㄱ</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -5213,7 +5213,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰∧
 㳞</t>
         </is>
       </c>
@@ -5222,21 +5222,21 @@
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太∧
 仲</t>
         </is>
       </c>
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃
+          <t xml:space="preserve">黃ʒ
 㑲黃</t>
         </is>
       </c>
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太∧
 仲</t>
         </is>
       </c>
@@ -5245,14 +5245,14 @@
       <c r="M5" s="24"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太∧
 仲</t>
         </is>
       </c>
       <c r="O5" s="24"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃
+          <t xml:space="preserve">黃ʒ
 㑲黃</t>
         </is>
       </c>
@@ -5276,7 +5276,7 @@
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄱ</t>
         </is>
       </c>
       <c r="G6" s="22"/>
@@ -5288,7 +5288,7 @@
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄱ</t>
         </is>
       </c>
       <c r="K6" s="22"/>
@@ -5301,7 +5301,7 @@
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄱ</t>
         </is>
       </c>
       <c r="O6" s="22"/>
@@ -5329,7 +5329,8 @@
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林
+⌝</t>
         </is>
       </c>
       <c r="G7" s="23"/>
@@ -5337,7 +5338,8 @@
       <c r="I7" s="23"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林
+⌝</t>
         </is>
       </c>
       <c r="K7" s="23"/>
@@ -5349,7 +5351,8 @@
       <c r="M7" s="23"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林
+⌝</t>
         </is>
       </c>
       <c r="O7" s="23"/>
@@ -5373,21 +5376,21 @@
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太⌝
 㑲</t>
         </is>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太∧
 仲</t>
         </is>
       </c>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太⌝
 㑲</t>
         </is>
       </c>
@@ -5400,14 +5403,14 @@
       <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太⌝
 㑲</t>
         </is>
       </c>
       <c r="O8" s="24"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太∧
 仲</t>
         </is>
       </c>
@@ -5424,7 +5427,7 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="E9" s="22"/>
@@ -5436,7 +5439,7 @@
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄱ</t>
         </is>
       </c>
       <c r="I9" s="22"/>
@@ -5448,7 +5451,7 @@
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄱ</t>
         </is>
       </c>
       <c r="M9" s="22"/>
@@ -5460,14 +5463,18 @@
       <c r="O9" s="22"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㄱ</t>
         </is>
       </c>
       <c r="Q9" s="22"/>
     </row>
     <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
-      <c r="B10" s="21"/>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
@@ -5526,49 +5533,53 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-–</t>
+          <t xml:space="preserve">㳞ʒ
+–
+ﾉ</t>
         </is>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲</t>
+仲ʒ
+ﾉ</t>
         </is>
       </c>
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-–</t>
+          <t xml:space="preserve">仲ʒ
+–ﾉ</t>
         </is>
       </c>
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲</t>
+仲ʒ
+ﾉ</t>
         </is>
       </c>
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-–</t>
+          <t xml:space="preserve">仲ʒ
+–
+ﾉ</t>
         </is>
       </c>
       <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-仲</t>
+仲ʒ</t>
         </is>
       </c>
       <c r="O11" s="24"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
+          <t xml:space="preserve">仲ʒ
 –</t>
         </is>
       </c>
@@ -5578,20 +5589,21 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㄷ</t>
         </is>
       </c>
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰⌝
 南</t>
         </is>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">太ㅋ
+∽</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -5604,20 +5616,21 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">太ㅋ∽</t>
         </is>
       </c>
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太⌝
 㑲</t>
         </is>
       </c>
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">太ㅋ
+∽</t>
         </is>
       </c>
       <c r="O12" s="22"/>
@@ -5671,8 +5684,8 @@
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-南</t>
+          <t xml:space="preserve">潢ʒ
+南ㄴ</t>
         </is>
       </c>
       <c r="E14" s="24"/>
@@ -5680,7 +5693,7 @@
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">潢ʒ
 㑲黃</t>
         </is>
       </c>
@@ -5694,7 +5707,7 @@
       <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃
+          <t xml:space="preserve">黃ʒ
 㑲黃</t>
         </is>
       </c>
@@ -5703,7 +5716,7 @@
       <c r="O14" s="24"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">潢ʒ
 㑲黃</t>
         </is>
       </c>
@@ -5784,7 +5797,7 @@
       <c r="J18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–潢</t>
+–潢ʒ</t>
         </is>
       </c>
       <c r="K18" s="23"/>
@@ -5793,7 +5806,7 @@
       <c r="N18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–潢</t>
+–潢ʒ</t>
         </is>
       </c>
       <c r="O18" s="23"/>
@@ -5845,7 +5858,7 @@
       <c r="I20" s="22"/>
       <c r="J20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㄷ</t>
         </is>
       </c>
       <c r="K20" s="22"/>
@@ -5858,7 +5871,7 @@
       <c r="M20" s="22"/>
       <c r="N20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㄷ</t>
         </is>
       </c>
       <c r="O20" s="22"/>
@@ -5882,22 +5895,24 @@
       <c r="I21" s="23"/>
       <c r="J21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-–</t>
+          <t xml:space="preserve">潢ʒ
+–
+ﾉ</t>
         </is>
       </c>
       <c r="K21" s="23"/>
       <c r="L21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–</t>
+–Z∧</t>
         </is>
       </c>
       <c r="M21" s="23"/>
       <c r="N21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-–</t>
+          <t xml:space="preserve">潢ʒ
+–
+ﾉ</t>
         </is>
       </c>
       <c r="O21" s="23"/>
@@ -5921,7 +5936,7 @@
       <c r="I22" s="24"/>
       <c r="J22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南⌝
 姑</t>
         </is>
       </c>
@@ -5935,14 +5950,14 @@
       <c r="M22" s="24"/>
       <c r="N22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南⌝
 姑</t>
         </is>
       </c>
       <c r="O22" s="24"/>
       <c r="P22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南∧
 潢</t>
         </is>
       </c>
@@ -5960,7 +5975,7 @@
       <c r="I23" s="22"/>
       <c r="J23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南潢
+          <t xml:space="preserve">南潢ㅂ
 –</t>
         </is>
       </c>
@@ -5999,7 +6014,7 @@
       <c r="J24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–㴌
-潢</t>
+潢ﾉ</t>
         </is>
       </c>
       <c r="K24" s="23"/>
@@ -6011,7 +6026,8 @@
       <c r="M24" s="23"/>
       <c r="N24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">Z∧
+潢</t>
         </is>
       </c>
       <c r="O24" s="23"/>
@@ -6035,28 +6051,28 @@
       <c r="J25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-∼</t>
+ㅂ∼</t>
         </is>
       </c>
       <c r="K25" s="24"/>
       <c r="L25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-–</t>
+          <t xml:space="preserve">潢ʒ
+–ﾉ</t>
         </is>
       </c>
       <c r="M25" s="24"/>
       <c r="N25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢</t>
+潢ʒ</t>
         </is>
       </c>
       <c r="O25" s="24"/>
       <c r="P25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-–</t>
+          <t xml:space="preserve">潢ʒ
+–ﾉ</t>
         </is>
       </c>
       <c r="Q25" s="24"/>
@@ -6073,27 +6089,27 @@
       <c r="I26" s="22"/>
       <c r="J26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢∼</t>
+          <t xml:space="preserve">潢ﾉ
+潢ㅂ∼</t>
         </is>
       </c>
       <c r="K26" s="22"/>
       <c r="L26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南⌝
 姑</t>
         </is>
       </c>
       <c r="M26" s="22"/>
       <c r="N26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南∽</t>
         </is>
       </c>
       <c r="O26" s="22"/>
       <c r="P26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南⌝
 姑</t>
         </is>
       </c>
@@ -6111,7 +6127,7 @@
       <c r="I27" s="23"/>
       <c r="J27" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南ㅂ</t>
         </is>
       </c>
       <c r="K27" s="23"/>
@@ -6149,7 +6165,7 @@
       <c r="K28" s="24"/>
       <c r="L28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
+          <t xml:space="preserve">南⌝
 姑</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/한오백년.xlsx
+++ b/sheets/조재수대금교본/검수/한오백년.xlsx
@@ -5087,28 +5087,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="15.29" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="64.52" customHeight="true">
+    <row r="2" ht="81.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="96.05" customHeight="true">
+    <row r="3" ht="121.67" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="96.05" customHeight="true">
+    <row r="4" ht="121.67" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -5209,7 +5209,7 @@
       <c r="P4" s="21"/>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="96.05" customHeight="true">
+    <row r="5" ht="121.67" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="96.05" customHeight="true">
+    <row r="6" ht="121.67" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="96.05" customHeight="true">
+    <row r="7" ht="121.67" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
       <c r="P7" s="21"/>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="96.05" customHeight="true">
+    <row r="8" ht="121.67" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="96.05" customHeight="true">
+    <row r="9" ht="121.67" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="96.05" customHeight="true">
+    <row r="10" ht="121.67" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="96.05" customHeight="true">
+    <row r="11" ht="121.67" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="96.05" customHeight="true">
+    <row r="12" ht="121.67" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="96.05" customHeight="true">
+    <row r="13" ht="121.67" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -5673,7 +5673,7 @@
       <c r="P13" s="21"/>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="96.05" customHeight="true">
+    <row r="14" ht="121.67" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="64.52" customHeight="true">
+    <row r="16" ht="81.63" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
       <c r="P16" s="20"/>
       <c r="Q16" s="20"/>
     </row>
-    <row r="17" ht="96.05" customHeight="true">
+    <row r="17" ht="121.67" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="Q17" s="22"/>
     </row>
-    <row r="18" ht="96.05" customHeight="true">
+    <row r="18" ht="121.67" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="Q18" s="23"/>
     </row>
-    <row r="19" ht="96.05" customHeight="true">
+    <row r="19" ht="121.67" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="24"/>
@@ -5846,7 +5846,7 @@
       <c r="P19" s="21"/>
       <c r="Q19" s="24"/>
     </row>
-    <row r="20" ht="96.05" customHeight="true">
+    <row r="20" ht="121.67" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="Q20" s="22"/>
     </row>
-    <row r="21" ht="96.05" customHeight="true">
+    <row r="21" ht="121.67" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Q21" s="23"/>
     </row>
-    <row r="22" ht="96.05" customHeight="true">
+    <row r="22" ht="121.67" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="Q22" s="24"/>
     </row>
-    <row r="23" ht="96.05" customHeight="true">
+    <row r="23" ht="121.67" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="Q23" s="22"/>
     </row>
-    <row r="24" ht="96.05" customHeight="true">
+    <row r="24" ht="121.67" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="Q24" s="23"/>
     </row>
-    <row r="25" ht="96.05" customHeight="true">
+    <row r="25" ht="121.67" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="Q25" s="24"/>
     </row>
-    <row r="26" ht="96.05" customHeight="true">
+    <row r="26" ht="121.67" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="Q26" s="22"/>
     </row>
-    <row r="27" ht="96.05" customHeight="true">
+    <row r="27" ht="121.67" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="Q27" s="23"/>
     </row>
-    <row r="28" ht="96.05" customHeight="true">
+    <row r="28" ht="121.67" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -6182,7 +6182,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
